--- a/spreadsheet_codegen/examples/basic/template.xlsx
+++ b/spreadsheet_codegen/examples/basic/template.xlsx
@@ -641,7 +641,7 @@
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">          excel-codegen render -c &lt;配置&gt;.yaml -x template.xlsx --write-excel</t>
+          <t xml:space="preserve">          spreadsheet-codegen render -c &lt;配置&gt;.yaml -x template.xlsx --write-excel</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">      想确认表里的代码是不是已经过期：excel-codegen check -c &lt;配置&gt;.yaml</t>
+          <t xml:space="preserve">      想确认表里的代码是不是已经过期：spreadsheet-codegen check -c &lt;配置&gt;.yaml</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
     <row r="27">
       <c r="A27" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  命令      excel-codegen render -c examples/example.yaml -x examples/template.xlsx --write-excel --outdir examples/generated</t>
+          <t xml:space="preserve">  命令      spreadsheet-codegen render -c examples/example.yaml -x examples/template.xlsx --write-excel --outdir examples/generated</t>
         </is>
       </c>
     </row>
